--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="224">
   <si>
     <t xml:space="preserve">Definition</t>
   </si>
@@ -131,6 +131,15 @@
   </si>
   <si>
     <t xml:space="preserve">light-demanding,shade-tolerant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photosynthetic pathway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PhotosyntheticPathway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3,C4,CAM</t>
   </si>
   <si>
     <t xml:space="preserve">Duration of leaves (leaf lifespan)</t>
@@ -973,7 +982,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1031"/>
+  <dimension ref="A1:H1032"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="111.7"/>
@@ -1188,13 +1197,13 @@
         <v>38</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
@@ -1213,9 +1222,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1229,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1240,16 +1247,16 @@
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1260,16 +1267,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1288,49 +1295,47 @@
       <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="n">
@@ -1340,36 +1345,38 @@
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>20</v>
+      <c r="E19" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1382,32 +1389,35 @@
       <c r="C21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
@@ -1419,33 +1429,28 @@
       <c r="C23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="n">
@@ -1455,19 +1460,19 @@
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="n">
@@ -1477,18 +1482,20 @@
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="3"/>
+        <v>75</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="n">
         <v>0</v>
@@ -1497,18 +1504,18 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E27" s="5"/>
+      <c r="D27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="n">
         <v>0</v>
@@ -1526,7 +1533,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="3"/>
@@ -1537,16 +1544,16 @@
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="3"/>
@@ -1557,20 +1564,22 @@
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" s="3"/>
+      <c r="D30" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="5"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1584,26 +1593,26 @@
         <v>20</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>89</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -1619,7 +1628,7 @@
         <v>20</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -1628,16 +1637,16 @@
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -1646,15 +1655,17 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -1662,36 +1673,32 @@
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -1702,16 +1709,16 @@
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -1722,16 +1729,16 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -1742,16 +1749,16 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -1762,22 +1769,23 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>109</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="E41" s="3"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
@@ -1790,7 +1798,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="n">
@@ -1800,18 +1808,17 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="n">
         <v>0</v>
@@ -1829,7 +1836,7 @@
         <v>20</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -1840,16 +1847,16 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -1860,16 +1867,16 @@
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -1929,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -1940,36 +1947,36 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -1980,16 +1987,16 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2000,54 +2007,54 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D53" s="3"/>
+      <c r="D53" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -2058,16 +2065,16 @@
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -2078,54 +2085,54 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -2136,16 +2143,16 @@
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -2156,35 +2163,35 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
-      <c r="G61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>114</v>
-      </c>
+      <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="n">
@@ -2194,16 +2201,16 @@
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -2222,31 +2229,31 @@
       <c r="C64" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
+      <c r="D64" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>154</v>
-      </c>
+      <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="3"/>
     </row>
@@ -2280,50 +2287,50 @@
       <c r="C67" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E67" s="3"/>
+      <c r="D67" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E67" s="5"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="H67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="3"/>
+      <c r="H68" s="3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -2334,10 +2341,10 @@
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>20</v>
@@ -2354,16 +2361,16 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -2374,16 +2381,16 @@
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -2423,7 +2430,7 @@
         <v>20</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -2434,16 +2441,16 @@
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -2462,18 +2469,22 @@
       <c r="C76" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D76" s="3"/>
+      <c r="D76" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
+      <c r="G76" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>20</v>
@@ -2486,17 +2497,15 @@
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>185</v>
-      </c>
+      <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -2517,9 +2526,7 @@
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
-      <c r="G79" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G79" s="3"/>
       <c r="H79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2533,7 +2540,7 @@
         <v>20</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -2544,16 +2551,16 @@
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -2564,16 +2571,16 @@
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -2584,16 +2591,16 @@
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -2604,16 +2611,16 @@
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -2624,20 +2631,22 @@
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>201</v>
+        <v>72</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2651,7 +2660,7 @@
         <v>20</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -2660,16 +2669,16 @@
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -2678,16 +2687,16 @@
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -2696,16 +2705,16 @@
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -2723,7 +2732,7 @@
         <v>20</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -2732,40 +2741,36 @@
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D91" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="E91" s="3"/>
-      <c r="F91" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>215</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -2776,25 +2781,46 @@
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3732,6 +3758,7 @@
     <row r="1029" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1030" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1031" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1032" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="227">
   <si>
     <t xml:space="preserve">Definition</t>
   </si>
@@ -140,6 +140,15 @@
   </si>
   <si>
     <t xml:space="preserve">C3,C4,CAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wood porosity type (for woody angiosperms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WoodPorosityType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ring-porous,semi-ring-porous,diffuse-porous</t>
   </si>
   <si>
     <t xml:space="preserve">Duration of leaves (leaf lifespan)</t>
@@ -436,7 +445,7 @@
     <t xml:space="preserve">10-4 kg m-1 MPa-1 s-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum leaf hydraulic conductance</t>
+    <t xml:space="preserve">Maximum leaf hydraulic conductance (per leaf area)</t>
   </si>
   <si>
     <t xml:space="preserve">kleaf</t>
@@ -445,7 +454,7 @@
     <t xml:space="preserve">mmol m-2 s-1 MPa-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum whole-plant hydraulic conductance</t>
+    <t xml:space="preserve">Maximum whole-plant hydraulic conductance (per leaf area)</t>
   </si>
   <si>
     <t xml:space="preserve">kplant</t>
@@ -982,7 +991,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1032"/>
+  <dimension ref="A1:H1033"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="111.7"/>
@@ -1215,13 +1224,13 @@
         <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
@@ -1240,9 +1249,7 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1256,7 +1263,7 @@
         <v>20</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1267,16 +1274,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1287,16 +1294,16 @@
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1315,49 +1322,47 @@
       <c r="C17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="n">
@@ -1367,36 +1372,38 @@
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>20</v>
+      <c r="E20" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="3"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1409,32 +1416,35 @@
       <c r="C22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
@@ -1446,33 +1456,28 @@
       <c r="C24" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="F24" s="3"/>
-      <c r="G24" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="n">
@@ -1482,19 +1487,19 @@
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="n">
@@ -1504,18 +1509,20 @@
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="3"/>
+        <v>78</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="n">
         <v>0</v>
@@ -1524,18 +1531,18 @@
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="5"/>
+      <c r="D28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -1553,7 +1560,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="3"/>
@@ -1564,16 +1571,16 @@
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="3"/>
@@ -1584,20 +1591,22 @@
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="3"/>
+      <c r="D31" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="5"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1611,26 +1620,26 @@
         <v>20</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>92</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -1646,7 +1655,7 @@
         <v>20</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -1655,16 +1664,16 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -1673,15 +1682,17 @@
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -1689,36 +1700,32 @@
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -1729,16 +1736,16 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -1749,16 +1756,16 @@
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -1769,16 +1776,16 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -1789,22 +1796,23 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>112</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="E42" s="3"/>
       <c r="F42" s="3"/>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
@@ -1817,7 +1825,7 @@
         <v>20</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="n">
@@ -1827,18 +1835,17 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="n">
         <v>0</v>
@@ -1856,7 +1863,7 @@
         <v>20</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -1867,16 +1874,16 @@
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -1887,16 +1894,16 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -1956,7 +1963,7 @@
         <v>20</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -1967,36 +1974,36 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2007,16 +2014,16 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2027,54 +2034,54 @@
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D54" s="3"/>
+      <c r="D54" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -2085,16 +2092,16 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -2105,54 +2112,54 @@
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -2163,16 +2170,16 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -2183,35 +2190,35 @@
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="n">
@@ -2221,16 +2228,16 @@
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -2249,31 +2256,31 @@
       <c r="C65" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
+      <c r="D65" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>157</v>
-      </c>
+      <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="3"/>
     </row>
@@ -2307,50 +2314,50 @@
       <c r="C68" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E68" s="3"/>
+      <c r="D68" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E68" s="5"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="H68" s="3"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="3"/>
+      <c r="H69" s="3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -2361,10 +2368,10 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>20</v>
@@ -2381,16 +2388,16 @@
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -2401,16 +2408,16 @@
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>173</v>
+        <v>48</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -2450,7 +2457,7 @@
         <v>20</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>61</v>
+        <v>179</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -2461,16 +2468,16 @@
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -2489,18 +2496,22 @@
       <c r="C77" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D77" s="3"/>
+      <c r="D77" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H77" s="3"/>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>20</v>
@@ -2513,17 +2524,15 @@
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>188</v>
-      </c>
+      <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -2544,9 +2553,7 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
-      <c r="G80" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G80" s="3"/>
       <c r="H80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2560,7 +2567,7 @@
         <v>20</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -2571,16 +2578,16 @@
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -2591,16 +2598,16 @@
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -2611,16 +2618,16 @@
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -2631,16 +2638,16 @@
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -2651,20 +2658,22 @@
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2678,7 +2687,7 @@
         <v>20</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -2687,16 +2696,16 @@
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -2705,16 +2714,16 @@
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -2723,16 +2732,16 @@
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -2750,7 +2759,7 @@
         <v>20</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -2759,40 +2768,36 @@
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D92" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="E92" s="3"/>
-      <c r="F92" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
@@ -2803,25 +2808,46 @@
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="G94" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3759,6 +3785,7 @@
     <row r="1030" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1031" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1032" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1033" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -1696,7 +1696,9 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
+      <c r="H36" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="232">
   <si>
     <t xml:space="preserve">Definition</t>
   </si>
@@ -35,6 +35,12 @@
   </si>
   <si>
     <t xml:space="preserve">EquivalentUnits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AcceptedMethods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DefaultMethod</t>
   </si>
   <si>
     <t xml:space="preserve">AcceptedValues</t>
@@ -340,6 +346,9 @@
     <t xml:space="preserve">MPa</t>
   </si>
   <si>
+    <t xml:space="preserve">osmotic,pressure-volume</t>
+  </si>
+  <si>
     <t xml:space="preserve">Modulus of elasticity (capacity of the cell wall to resist changes in volume in response to changes in turgor) of leaves</t>
   </si>
   <si>
@@ -464,6 +473,12 @@
   </si>
   <si>
     <t xml:space="preserve">VCstem_P12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DH,CE,CA,AD,AS,AE,OV,MicroCT,Pn,MRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DH</t>
   </si>
   <si>
     <t xml:space="preserve">VCstem_P50</t>
@@ -991,7 +1006,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1033"/>
+  <dimension ref="A1:J1033"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="111.7"/>
@@ -999,9 +1014,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="8" style="1" width="11.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="41" style="1" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="12.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="10" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1027" min="43" style="1" width="12.76"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1029,1824 +1045,2064 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="3"/>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="3"/>
+      <c r="I16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
+      <c r="I17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
+      <c r="I19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+        <v>22</v>
+      </c>
       <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
-      <c r="G22" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="3"/>
+      <c r="I22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="n">
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
+        <v>77</v>
+      </c>
       <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F25" s="3"/>
-      <c r="G25" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="3"/>
+      <c r="I25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="F26" s="3"/>
-      <c r="G26" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="3"/>
+      <c r="I26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
+      <c r="I27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="3"/>
+      <c r="I28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
       <c r="H29" s="3"/>
+      <c r="I29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="3"/>
+      <c r="I30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="3"/>
+      <c r="I31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="F36" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="G36" s="3"/>
-      <c r="H36" s="3" t="n">
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3" t="n">
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3" t="n">
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H43" s="3"/>
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H44" s="3"/>
+      <c r="I44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G45" s="3"/>
       <c r="H45" s="3"/>
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
+      <c r="I46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G47" s="3"/>
       <c r="H47" s="3"/>
+      <c r="I47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-      <c r="G48" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
+      <c r="I48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
-      <c r="G49" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G49" s="3"/>
       <c r="H49" s="3"/>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
-      <c r="G50" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G50" s="3"/>
       <c r="H50" s="3"/>
+      <c r="I50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G51" s="3"/>
       <c r="H51" s="3"/>
+      <c r="I51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3" t="n">
+      <c r="F52" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3" t="n">
+      <c r="F53" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3" t="n">
+      <c r="F54" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
+      <c r="F55" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="H55" s="3"/>
+      <c r="I55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="G56" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3" t="n">
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3" t="n">
+      <c r="G57" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3" t="n">
+      <c r="G58" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3" t="n">
-        <v>0</v>
+      <c r="F59" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="H59" s="3"/>
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3" t="n">
+      <c r="F60" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3" t="n">
+      <c r="F61" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3" t="n">
+      <c r="F62" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
+      <c r="F63" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="H63" s="3"/>
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
-      <c r="G64" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G64" s="3"/>
       <c r="H64" s="3"/>
+      <c r="I64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G65" s="3"/>
       <c r="H65" s="3"/>
+      <c r="I65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3" t="n">
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="3"/>
+      <c r="J66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E67" s="5"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
       <c r="H67" s="3"/>
+      <c r="I67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E68" s="5"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
       <c r="H68" s="3"/>
+      <c r="I68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
-      <c r="G69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="3" t="n">
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G70" s="3"/>
       <c r="H70" s="3"/>
+      <c r="I70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3"/>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
-      <c r="G71" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G71" s="3"/>
       <c r="H71" s="3"/>
+      <c r="I71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-      <c r="G72" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G72" s="3"/>
       <c r="H72" s="3"/>
+      <c r="I72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G73" s="3"/>
       <c r="H73" s="3"/>
+      <c r="I73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
-      <c r="G74" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G74" s="3"/>
       <c r="H74" s="3"/>
+      <c r="I74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G75" s="3"/>
       <c r="H75" s="3"/>
+      <c r="I75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G76" s="3"/>
       <c r="H76" s="3"/>
+      <c r="I76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
-      <c r="G77" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G77" s="3"/>
       <c r="H77" s="3"/>
+      <c r="I77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3"/>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
-      <c r="G81" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G81" s="3"/>
       <c r="H81" s="3"/>
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
-      <c r="G82" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G82" s="3"/>
       <c r="H82" s="3"/>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
-      <c r="G83" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G83" s="3"/>
       <c r="H83" s="3"/>
+      <c r="I83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
-      <c r="G84" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G84" s="3"/>
       <c r="H84" s="3"/>
+      <c r="I84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
-      <c r="G85" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G85" s="3"/>
       <c r="H85" s="3"/>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
-      <c r="G86" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G86" s="3"/>
       <c r="H86" s="3"/>
+      <c r="I86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
-      <c r="F93" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="3" t="n">
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
-      <c r="F94" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="n">
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
-      <c r="G95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="3" t="n">
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="n">
         <v>5</v>
       </c>
     </row>

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="238">
   <si>
     <t xml:space="preserve">Definition</t>
   </si>
@@ -284,6 +284,24 @@
   </si>
   <si>
     <t xml:space="preserve">LeafWidth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stomatal area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StomatalArea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">um2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stomatal density per leaf area (total, including abaxial and adaxial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StomatalDensity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm-2</t>
   </si>
   <si>
     <t xml:space="preserve">Maximum stomatal conductance to water vapor</t>
@@ -1006,7 +1024,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1033"/>
+  <dimension ref="A1:J1035"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="111.7"/>
@@ -1631,12 +1649,12 @@
       <c r="C29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3" t="n">
         <v>0</v>
@@ -1653,12 +1671,12 @@
       <c r="C30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="D30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3" t="n">
         <v>0</v>
@@ -1667,16 +1685,16 @@
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -1689,24 +1707,24 @@
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G32" s="3"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1719,15 +1737,16 @@
       <c r="C33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G33" s="3"/>
+      <c r="D33" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1744,7 +1763,9 @@
         <v>103</v>
       </c>
       <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -1752,19 +1773,20 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -1772,39 +1794,37 @@
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -1814,19 +1834,21 @@
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -1836,38 +1858,34 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -1880,16 +1898,16 @@
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -1902,16 +1920,16 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -1927,55 +1945,58 @@
         <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>118</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>118</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+        <v>124</v>
+      </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3" t="n">
         <v>0</v>
@@ -1984,20 +2005,17 @@
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3" t="n">
         <v>0</v>
@@ -2006,16 +2024,16 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -2028,16 +2046,16 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -2050,16 +2068,16 @@
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2103,7 +2121,7 @@
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -2116,75 +2134,67 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="E52" s="3"/>
-      <c r="F52" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>142</v>
-      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
       <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="E53" s="3"/>
-      <c r="F53" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>142</v>
-      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -2194,47 +2204,49 @@
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="3"/>
+      <c r="D55" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H55" s="3"/>
-      <c r="I55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -2244,49 +2256,47 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -2296,47 +2306,49 @@
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="3"/>
+      <c r="D59" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="I59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -2346,49 +2358,47 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -2398,66 +2408,74 @@
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
+      <c r="F64" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="H64" s="3"/>
-      <c r="I64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3" t="n">
         <v>0</v>
@@ -2466,40 +2484,42 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
+      <c r="D66" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="D67" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -2508,23 +2528,21 @@
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D68" s="5" t="s">
-        <v>168</v>
-      </c>
+      <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="3"/>
     </row>
@@ -2538,36 +2556,34 @@
       <c r="C69" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="D69" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="J69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
+      <c r="D70" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3" t="n">
         <v>0</v>
@@ -2576,16 +2592,16 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -2594,20 +2610,22 @@
       <c r="I71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3"/>
+      <c r="J71" s="3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -2620,16 +2638,16 @@
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -2642,16 +2660,16 @@
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -2664,16 +2682,16 @@
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -2695,7 +2713,7 @@
         <v>22</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>66</v>
+        <v>187</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -2708,16 +2726,16 @@
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -2730,53 +2748,59 @@
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D78" s="3"/>
+      <c r="D78" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
+      <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J78" s="3"/>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D79" s="3"/>
+      <c r="D79" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
+      <c r="I79" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>196</v>
-      </c>
+      <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -2786,24 +2810,20 @@
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>199</v>
-      </c>
+      <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
-      <c r="I81" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I81" s="3"/>
       <c r="J81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2817,29 +2837,27 @@
         <v>22</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I82" s="3"/>
       <c r="J82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -2852,16 +2870,16 @@
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -2874,16 +2892,16 @@
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -2896,10 +2914,10 @@
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>22</v>
@@ -2918,56 +2936,60 @@
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
+      <c r="I87" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
+      <c r="I88" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -2978,16 +3000,16 @@
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -2998,16 +3020,16 @@
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -3018,16 +3040,16 @@
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -3038,27 +3060,23 @@
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D93" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
-      <c r="H93" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
@@ -3068,21 +3086,17 @@
         <v>229</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D94" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
-      <c r="H94" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
@@ -3092,22 +3106,68 @@
         <v>231</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>22</v>
+        <v>232</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
+      <c r="H95" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="I95" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J95" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4044,6 +4104,8 @@
     <row r="1031" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1032" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1033" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1034" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1035" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -286,10 +286,10 @@
     <t xml:space="preserve">LeafWidth</t>
   </si>
   <si>
-    <t xml:space="preserve">Stomatal area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StomatalArea</t>
+    <t xml:space="preserve">Stomatal size (area)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StomatalSize</t>
   </si>
   <si>
     <t xml:space="preserve">um2</t>

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="240">
   <si>
     <t xml:space="preserve">Definition</t>
   </si>
@@ -304,10 +304,10 @@
     <t xml:space="preserve">mm-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum stomatal conductance to water vapor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gswmax</t>
+    <t xml:space="preserve">Stomatal conductance to water vapor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gsw</t>
   </si>
   <si>
     <r>
@@ -341,6 +341,12 @@
       </rPr>
       <t xml:space="preserve">m-2</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum stomatal conductance to water vapor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gswmax</t>
   </si>
   <si>
     <t xml:space="preserve">Minimum stomatal conductance to water vapor</t>
@@ -1024,7 +1030,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1035"/>
+  <dimension ref="A1:J1036"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="111.7"/>
@@ -1696,9 +1702,9 @@
       <c r="D31" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="n">
         <v>0</v>
@@ -1759,33 +1765,34 @@
       <c r="C34" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G34" s="3"/>
+      <c r="D34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="E35" s="3"/>
+      <c r="F35" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -1803,10 +1810,11 @@
         <v>22</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -1814,16 +1822,16 @@
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -1843,18 +1851,14 @@
         <v>22</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="3" t="s">
-        <v>104</v>
-      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
@@ -1866,13 +1870,19 @@
       <c r="C39" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
+      <c r="J39" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
@@ -1884,30 +1894,26 @@
       <c r="C40" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -1920,16 +1926,16 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -1942,16 +1948,16 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -1964,16 +1970,16 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -1986,7 +1992,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>123</v>
@@ -1995,26 +2001,29 @@
         <v>22</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>124</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3" t="n">
@@ -2033,11 +2042,8 @@
         <v>22</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
+        <v>126</v>
+      </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3" t="n">
         <v>0</v>
@@ -2046,16 +2052,16 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -2077,7 +2083,7 @@
         <v>22</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2099,7 +2105,7 @@
         <v>22</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -2112,16 +2118,16 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -2134,16 +2140,16 @@
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2156,16 +2162,16 @@
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2187,40 +2193,36 @@
         <v>22</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="E54" s="3"/>
-      <c r="F54" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>148</v>
-      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
@@ -2230,23 +2232,23 @@
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -2256,31 +2258,33 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H57" s="3"/>
-      <c r="I57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>153</v>
@@ -2288,41 +2292,39 @@
       <c r="C58" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -2332,23 +2334,23 @@
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -2358,31 +2360,33 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H61" s="3"/>
-      <c r="I61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>158</v>
@@ -2390,41 +2394,39 @@
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -2434,23 +2436,23 @@
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -2460,31 +2462,33 @@
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D65" s="3"/>
+      <c r="D65" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="I65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>163</v>
@@ -2492,12 +2496,14 @@
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>129</v>
-      </c>
+      <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3" t="n">
         <v>0</v>
@@ -2515,7 +2521,7 @@
         <v>22</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -2528,21 +2534,23 @@
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C68" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3"/>
     </row>
@@ -2556,30 +2564,28 @@
       <c r="C69" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D69" s="5" t="s">
-        <v>171</v>
-      </c>
+      <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
@@ -2592,27 +2598,25 @@
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="J71" s="3"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
@@ -2625,7 +2629,7 @@
         <v>22</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>57</v>
+        <v>168</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -2634,7 +2638,9 @@
       <c r="I72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3"/>
+      <c r="J72" s="3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
@@ -2647,7 +2653,7 @@
         <v>22</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -2669,7 +2675,7 @@
         <v>22</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -2713,7 +2719,7 @@
         <v>22</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -2726,16 +2732,16 @@
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -2748,16 +2754,16 @@
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -2779,7 +2785,7 @@
         <v>22</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -2792,20 +2798,24 @@
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
+      <c r="I80" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2836,9 +2846,7 @@
       <c r="C82" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>202</v>
-      </c>
+      <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -2848,38 +2856,36 @@
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
-      <c r="I83" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" s="3"/>
       <c r="J83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -2901,7 +2907,7 @@
         <v>22</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -2923,7 +2929,7 @@
         <v>22</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -2989,27 +2995,29 @@
         <v>22</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
+      <c r="I89" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J89" s="3"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -3029,7 +3037,7 @@
         <v>22</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -3049,7 +3057,7 @@
         <v>22</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -3069,7 +3077,7 @@
         <v>22</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -3080,16 +3088,16 @@
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -3106,38 +3114,34 @@
         <v>231</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D95" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>0</v>
@@ -3154,21 +3158,44 @@
         <v>237</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
+      <c r="H97" s="3" t="s">
+        <v>235</v>
+      </c>
       <c r="I97" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J97" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4106,6 +4133,7 @@
     <row r="1033" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1034" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1035" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1036" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="243">
   <si>
     <t xml:space="preserve">Definition</t>
   </si>
@@ -302,6 +302,15 @@
   </si>
   <si>
     <t xml:space="preserve">mm-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leaf vein density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LeafVeinDensity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm mm-2</t>
   </si>
   <si>
     <t xml:space="preserve">Stomatal conductance to water vapor</t>
@@ -1030,7 +1039,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1036"/>
+  <dimension ref="A1:J1037"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="111.7"/>
@@ -1699,7 +1708,7 @@
       <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E31" s="3"/>
@@ -1722,11 +1731,11 @@
         <v>22</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="n">
         <v>0</v>
@@ -1735,16 +1744,16 @@
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -1757,16 +1766,16 @@
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -1779,41 +1788,42 @@
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G35" s="3"/>
+      <c r="D35" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
@@ -1822,19 +1832,20 @@
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -1851,7 +1862,7 @@
         <v>22</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -1862,80 +1873,78 @@
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="3"/>
+      <c r="D40" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
+      <c r="F40" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
+      <c r="J40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -1948,16 +1957,16 @@
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -1970,16 +1979,16 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -1992,16 +2001,16 @@
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -2014,22 +2023,25 @@
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>126</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
-      <c r="I46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
@@ -2042,7 +2054,7 @@
         <v>22</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3" t="n">
@@ -2052,20 +2064,17 @@
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -2083,7 +2092,7 @@
         <v>22</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2096,16 +2105,16 @@
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -2118,16 +2127,16 @@
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -2193,7 +2202,7 @@
         <v>22</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -2206,33 +2215,29 @@
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="E55" s="3"/>
-      <c r="F55" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>150</v>
-      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>151</v>
@@ -2241,14 +2246,14 @@
         <v>22</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -2258,23 +2263,23 @@
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -2284,73 +2289,73 @@
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -2360,23 +2365,23 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -2386,73 +2391,73 @@
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -2462,23 +2467,23 @@
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -2488,44 +2493,48 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="I66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -2534,16 +2543,16 @@
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -2564,35 +2573,35 @@
       <c r="C69" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="D69" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>173</v>
-      </c>
+      <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="3"/>
     </row>
@@ -2628,32 +2637,30 @@
       <c r="C72" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
+      <c r="D72" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="J72" s="3"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -2662,20 +2669,22 @@
       <c r="I73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3"/>
+      <c r="J73" s="3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -2688,16 +2697,16 @@
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -2710,10 +2719,10 @@
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>22</v>
@@ -2732,16 +2741,16 @@
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -2785,7 +2794,7 @@
         <v>22</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -2798,16 +2807,16 @@
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>197</v>
+        <v>66</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -2828,20 +2837,24 @@
       <c r="C81" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D81" s="3"/>
+      <c r="D81" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
+      <c r="I81" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>22</v>
@@ -2856,17 +2869,15 @@
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>204</v>
-      </c>
+      <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -2891,9 +2902,7 @@
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
-      <c r="I84" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I84" s="3"/>
       <c r="J84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2907,7 +2916,7 @@
         <v>22</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -2920,16 +2929,16 @@
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -2942,16 +2951,16 @@
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -2964,10 +2973,10 @@
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>22</v>
@@ -2986,10 +2995,10 @@
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>22</v>
@@ -3008,22 +3017,24 @@
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
+      <c r="I90" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J90" s="3"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3037,7 +3048,7 @@
         <v>22</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -3048,16 +3059,16 @@
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -3068,16 +3079,16 @@
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -3088,16 +3099,16 @@
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -3117,7 +3128,7 @@
         <v>22</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -3128,44 +3139,40 @@
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D96" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
       <c r="H97" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I97" s="3" t="n">
         <v>0</v>
@@ -3176,27 +3183,50 @@
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>22</v>
+        <v>237</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
+      <c r="H98" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="I98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4134,6 +4164,7 @@
     <row r="1034" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1035" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1036" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1037" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="250">
   <si>
     <t xml:space="preserve">Definition</t>
   </si>
@@ -302,6 +302,27 @@
   </si>
   <si>
     <t xml:space="preserve">mm-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stomatal surface area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StomatalArea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stomatal length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StomatalLength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">um</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stomatal width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StomatalWidth</t>
   </si>
   <si>
     <t xml:space="preserve">Leaf vein density</t>
@@ -1039,7 +1060,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1037"/>
+  <dimension ref="A1:J1040"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="111.7"/>
@@ -1709,7 +1730,7 @@
         <v>22</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1722,16 +1743,16 @@
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -1744,20 +1765,20 @@
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="C33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="D33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="n">
         <v>0</v>
@@ -1766,20 +1787,20 @@
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="n">
         <v>0</v>
@@ -1797,11 +1818,11 @@
         <v>22</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+        <v>106</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3" t="n">
         <v>0</v>
@@ -1810,82 +1831,87 @@
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G36" s="3"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="C37" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G37" s="3"/>
+      <c r="D37" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="I37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="C38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="D38" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="I38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="E39" s="3"/>
+      <c r="F39" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -1902,18 +1928,15 @@
         <v>22</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>115</v>
+      </c>
       <c r="F40" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
@@ -1925,7 +1948,9 @@
       <c r="C41" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="3"/>
+      <c r="D41" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -1935,41 +1960,41 @@
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -1979,38 +2004,34 @@
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -2023,16 +2044,16 @@
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -2045,45 +2066,51 @@
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
-      <c r="I48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>133</v>
@@ -2092,33 +2119,30 @@
         <v>22</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3" t="n">
         <v>0</v>
@@ -2136,11 +2160,8 @@
         <v>22</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+        <v>136</v>
+      </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3" t="n">
         <v>0</v>
@@ -2180,7 +2201,7 @@
         <v>22</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2193,16 +2214,16 @@
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="C54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -2215,16 +2236,16 @@
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -2237,125 +2258,115 @@
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="E56" s="3"/>
-      <c r="F56" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
       <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="E57" s="3"/>
-      <c r="F57" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
       <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="E58" s="3"/>
-      <c r="F58" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
       <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="3"/>
+      <c r="D59" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="I59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>157</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -2368,20 +2379,20 @@
         <v>157</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -2394,70 +2405,70 @@
         <v>157</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -2467,23 +2478,23 @@
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -2493,101 +2504,109 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="3"/>
+      <c r="D67" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="I67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
+      <c r="F68" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="H68" s="3"/>
-      <c r="I68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
         <v>169</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="H69" s="3"/>
-      <c r="I69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>173</v>
@@ -2595,13 +2614,17 @@
       <c r="C70" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3"/>
     </row>
@@ -2615,12 +2638,12 @@
       <c r="C71" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
+      <c r="D71" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3" t="n">
         <v>0</v>
@@ -2629,20 +2652,20 @@
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3" t="n">
         <v>0</v>
@@ -2651,44 +2674,40 @@
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="C73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>100</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D74" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3" t="n">
         <v>0</v>
@@ -2705,12 +2724,12 @@
       <c r="C75" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
+      <c r="D75" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -2719,16 +2738,16 @@
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -2737,20 +2756,22 @@
       <c r="I76" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3"/>
+      <c r="J76" s="3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -2763,16 +2784,16 @@
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -2794,7 +2815,7 @@
         <v>22</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -2807,16 +2828,16 @@
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="C80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -2829,16 +2850,16 @@
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -2851,20 +2872,24 @@
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
+      <c r="I82" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2877,12 +2902,16 @@
       <c r="C83" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D83" s="3"/>
+      <c r="D83" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
+      <c r="I83" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2902,7 +2931,9 @@
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
+      <c r="I84" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2915,60 +2946,50 @@
       <c r="C85" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>210</v>
-      </c>
+      <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
-      <c r="I85" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I85" s="3"/>
       <c r="J85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="C86" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>210</v>
-      </c>
+      <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
-      <c r="I86" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" s="3"/>
       <c r="J86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
-      <c r="I87" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I87" s="3"/>
       <c r="J87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2982,7 +3003,7 @@
         <v>22</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -2995,16 +3016,16 @@
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -3017,16 +3038,16 @@
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -3039,22 +3060,24 @@
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
+      <c r="I91" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3068,13 +3091,15 @@
         <v>22</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
+      <c r="I92" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3088,13 +3113,15 @@
         <v>22</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
+      <c r="I93" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3108,7 +3135,7 @@
         <v>22</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -3119,16 +3146,16 @@
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -3148,7 +3175,7 @@
         <v>22</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -3165,71 +3192,128 @@
         <v>236</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D97" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
-      <c r="H97" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H97" s="3"/>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3"/>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
-      <c r="H98" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="I98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="C99" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D99" s="3"/>
+      <c r="D99" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
-      <c r="I99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="3" t="n">
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4165,6 +4249,9 @@
     <row r="1035" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1036" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1037" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1038" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1039" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1040" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
